--- a/total_leave_1.xlsx
+++ b/total_leave_1.xlsx
@@ -523,7 +523,7 @@
         <v>35</v>
       </c>
       <c r="D2" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -537,7 +537,7 @@
         <v>35</v>
       </c>
       <c r="D3" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -551,7 +551,7 @@
         <v>35</v>
       </c>
       <c r="D4" s="2">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -565,7 +565,7 @@
         <v>35</v>
       </c>
       <c r="D5" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -579,7 +579,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -593,7 +593,7 @@
         <v>35</v>
       </c>
       <c r="D7" s="2">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -607,7 +607,7 @@
         <v>35</v>
       </c>
       <c r="D8" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -621,7 +621,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -635,7 +635,7 @@
         <v>35</v>
       </c>
       <c r="D10" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -649,7 +649,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -663,7 +663,7 @@
         <v>35</v>
       </c>
       <c r="D12" s="2">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -677,7 +677,7 @@
         <v>35</v>
       </c>
       <c r="D13" s="1">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -691,7 +691,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="1">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -705,7 +705,7 @@
         <v>35</v>
       </c>
       <c r="D15" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -719,7 +719,7 @@
         <v>35</v>
       </c>
       <c r="D16" s="1">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -733,7 +733,7 @@
         <v>35</v>
       </c>
       <c r="D17" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -747,7 +747,7 @@
         <v>35</v>
       </c>
       <c r="D18" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -761,7 +761,7 @@
         <v>35</v>
       </c>
       <c r="D19" s="1">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -789,7 +789,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -803,7 +803,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="1">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -817,7 +817,7 @@
         <v>35</v>
       </c>
       <c r="D23" s="1">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">

--- a/total_leave_1.xlsx
+++ b/total_leave_1.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="38">
   <si>
     <t>employee_email</t>
   </si>
@@ -146,13 +146,16 @@
   </si>
   <si>
     <t>carryforward_days</t>
+  </si>
+  <si>
+    <t>AvailableLeave</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +168,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFEBC88D"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -202,13 +211,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="15.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" customWidth="1"/>
@@ -498,7 +510,7 @@
     <col min="4" max="4" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -511,8 +523,11 @@
       <c r="D1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E1" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>16001</v>
       </c>
@@ -525,8 +540,11 @@
       <c r="D2" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>16008</v>
       </c>
@@ -539,8 +557,11 @@
       <c r="D3" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E3">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>16018</v>
       </c>
@@ -553,8 +574,11 @@
       <c r="D4" s="2">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>16052</v>
       </c>
@@ -567,8 +591,11 @@
       <c r="D5" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>16060</v>
       </c>
@@ -581,8 +608,11 @@
       <c r="D6" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>16063</v>
       </c>
@@ -595,8 +625,11 @@
       <c r="D7" s="2">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>16076</v>
       </c>
@@ -609,8 +642,11 @@
       <c r="D8" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>16079</v>
       </c>
@@ -623,8 +659,11 @@
       <c r="D9" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>16080</v>
       </c>
@@ -637,8 +676,11 @@
       <c r="D10" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E10">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>16081</v>
       </c>
@@ -651,8 +693,11 @@
       <c r="D11" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E11">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>16082</v>
       </c>
@@ -665,8 +710,11 @@
       <c r="D12" s="2">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>16083</v>
       </c>
@@ -679,8 +727,11 @@
       <c r="D13" s="1">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E13">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>16084</v>
       </c>
@@ -693,8 +744,11 @@
       <c r="D14" s="1">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E14">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>16088</v>
       </c>
@@ -707,8 +761,11 @@
       <c r="D15" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E15">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>16089</v>
       </c>
@@ -721,8 +778,11 @@
       <c r="D16" s="1">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E16">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16090</v>
       </c>
@@ -735,8 +795,11 @@
       <c r="D17" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E17">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16092</v>
       </c>
@@ -749,8 +812,11 @@
       <c r="D18" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E18">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16095</v>
       </c>
@@ -763,8 +829,11 @@
       <c r="D19" s="1">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E19">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>16099</v>
       </c>
@@ -777,8 +846,11 @@
       <c r="D20" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>16104</v>
       </c>
@@ -791,8 +863,11 @@
       <c r="D21" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E21">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>16109</v>
       </c>
@@ -805,8 +880,11 @@
       <c r="D22" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E22">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>16110</v>
       </c>
@@ -819,8 +897,11 @@
       <c r="D23" s="1">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E23">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>16142</v>
       </c>
@@ -833,8 +914,11 @@
       <c r="D24" s="1">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E24">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>16120</v>
       </c>
@@ -847,8 +931,11 @@
       <c r="D25" s="1">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E25">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>16121</v>
       </c>
@@ -861,8 +948,11 @@
       <c r="D26" s="1">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E26">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>16122</v>
       </c>
@@ -875,8 +965,11 @@
       <c r="D27" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E27">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>16124</v>
       </c>
@@ -889,8 +982,11 @@
       <c r="D28" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E28">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>16125</v>
       </c>
@@ -903,8 +999,11 @@
       <c r="D29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E29">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>16127</v>
       </c>
@@ -917,8 +1016,11 @@
       <c r="D30" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E30">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>16128</v>
       </c>
@@ -931,8 +1033,11 @@
       <c r="D31" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E31">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>16130</v>
       </c>
@@ -945,8 +1050,11 @@
       <c r="D32" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E32">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>16131</v>
       </c>
@@ -959,8 +1067,12 @@
       <c r="D33" s="1">
         <v>1.5</v>
       </c>
+      <c r="E33">
+        <v>5.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>